--- a/Dashboards/data/Data final/ingresos/ingresos_edad.xlsx
+++ b/Dashboards/data/Data final/ingresos/ingresos_edad.xlsx
@@ -1339,7 +1339,7 @@
         <v>2021</v>
       </c>
       <c r="C70" t="n">
-        <v>150.53</v>
+        <v>157.17</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>2021</v>
       </c>
       <c r="C71" t="n">
-        <v>211.64</v>
+        <v>213.98</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         <v>2021</v>
       </c>
       <c r="C72" t="n">
-        <v>243.54</v>
+        <v>245.16</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>2021</v>
       </c>
       <c r="C73" t="n">
-        <v>268.85</v>
+        <v>270.66</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>2022</v>
       </c>
       <c r="C74" t="n">
-        <v>161.22</v>
+        <v>163.16</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>2022</v>
       </c>
       <c r="C75" t="n">
-        <v>224.33</v>
+        <v>224.31</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>2022</v>
       </c>
       <c r="C76" t="n">
-        <v>260.46</v>
+        <v>262.25</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>2022</v>
       </c>
       <c r="C77" t="n">
-        <v>287.34</v>
+        <v>288.74</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>2023</v>
       </c>
       <c r="C78" t="n">
-        <v>156.33</v>
+        <v>157.39</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>2023</v>
       </c>
       <c r="C79" t="n">
-        <v>220.23</v>
+        <v>223.48</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         <v>2023</v>
       </c>
       <c r="C80" t="n">
-        <v>261.06</v>
+        <v>262.15</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>288.62</v>
+        <v>276.99</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1495,7 @@
         <v>2024</v>
       </c>
       <c r="C82" t="n">
-        <v>152.55</v>
+        <v>148.44</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         <v>2024</v>
       </c>
       <c r="C83" t="n">
-        <v>216.69</v>
+        <v>211.39</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1521,7 @@
         <v>2024</v>
       </c>
       <c r="C84" t="n">
-        <v>261.06</v>
+        <v>252.29</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>2024</v>
       </c>
       <c r="C85" t="n">
-        <v>305.96</v>
+        <v>277.19</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>165.57</v>
+        <v>173.13</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         <v>2025</v>
       </c>
       <c r="C87" t="n">
-        <v>234.82</v>
+        <v>244.35</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         <v>2025</v>
       </c>
       <c r="C88" t="n">
-        <v>273.56</v>
+        <v>289.03</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         <v>2025</v>
       </c>
       <c r="C89" t="n">
-        <v>313.42</v>
+        <v>329.87</v>
       </c>
     </row>
   </sheetData>
